--- a/basedatos_partidas/salida/descompuestos/CT-08-04-030.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-08-04-030.xlsx
@@ -565,10 +565,10 @@
         <v>0.1</v>
       </c>
       <c r="G11" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="H11" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>5.82</v>
+        <v>6.42</v>
       </c>
     </row>
     <row r="13">
@@ -724,7 +724,7 @@
         <v>1</v>
       </c>
       <c r="G21" t="n">
-        <v>9.85</v>
+        <v>10.45</v>
       </c>
       <c r="H21" t="n">
         <v>0.1</v>
@@ -743,7 +743,7 @@
       </c>
       <c r="G22" s="4" t="n"/>
       <c r="H22" s="5" t="n">
-        <v>9.949999999999999</v>
+        <v>10.55</v>
       </c>
     </row>
   </sheetData>

--- a/basedatos_partidas/salida/descompuestos/CT-08-04-030.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-08-04-030.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A3:H22"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -451,6 +451,20 @@
     <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Capítulo: 08 Pisos y pavimentos</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Subcapítulo: Pisos de madera y laminados</t>
+        </is>
+      </c>
+    </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>

--- a/basedatos_partidas/salida/descompuestos/CT-08-04-030.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-08-04-030.xlsx
@@ -478,14 +478,14 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>Piso de parquet encolado sobre contrapiso.</t>
+          <t>Piso de parquet encolado sobre afirmado.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Colocación de parquet encolado directamente sobre el contrapiso con adhesivo de poliuretano, sin rastreles. Exige un contrapiso perfectamente plano, seco y sin humedad residual: el parquet encolado sobre una base húmeda se abomba y se despega sin remedio, por lo que la medición de humedad del soporte antes de colocar no es un trámite sino la condición del trabajo. Incluye la comprobación de planitud y humedad, la imprimación del soporte si el adhesivo la requiere, el replanteo del despiece, el encolado y colocación con presión, la junta perimetral y el retiro de restos de adhesivo. No incluye el lijado y barnizado. El parquet lo elige el cliente y se presupuesta aparte. Medido en superficie realmente ejecutada, descontando huecos mayores de 1 m².
+          <t xml:space="preserve">Colocación de parquet encolado directamente sobre el afirmado con adhesivo de poliuretano, sin rastreles. Exige un afirmado perfectamente plano, seco y sin humedad residual: el parquet encolado sobre una base húmeda se abomba y se despega sin remedio, por lo que la medición de humedad del soporte antes de colocar no es un trámite sino la condición del trabajo. Incluye la comprobación de planitud y humedad, la imprimación del soporte si el adhesivo la requiere, el replanteo del despiece, el encolado y colocación con presión, la junta perimetral y el retiro de restos de adhesivo. No incluye el lijado y barnizado. El parquet lo elige el cliente y se presupuesta aparte. Medido en superficie realmente ejecutada, descontando huecos mayores de 1 m².
 </t>
         </is>
       </c>
@@ -546,7 +546,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Adhesivo de poliuretano para encolado de parquet y madera sobre contrapiso.</t>
+          <t>Adhesivo de poliuretano para encolado de parquet y madera sobre afirmado.</t>
         </is>
       </c>
       <c r="F10" t="n">
